--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.75</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AA5" t="n">
         <v>1.74</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.75</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AA5" t="n">
         <v>1.74</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.75</v>
       </c>
-      <c r="N4" t="n">
+      <c r="AA4" t="n">
         <v>1.74</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.75</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AA5" t="n">
         <v>1.74</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z5" t="n">
         <v>3.75</v>
       </c>
-      <c r="N5" t="n">
+      <c r="AA5" t="n">
         <v>1.74</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -680,13 +680,13 @@
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>2.47</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V2" t="n">
         <v>6.1</v>
@@ -704,10 +704,10 @@
         <v>3.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>2.7</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -671,16 +671,16 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
         <v>2.47</v>
@@ -698,10 +698,10 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76</v>
@@ -716,7 +716,7 @@
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
         <v>2.24</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.75</v>
       </c>
-      <c r="N4" t="n">
+      <c r="AA4" t="n">
         <v>1.74</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.62</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -817,34 +817,34 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>2.91</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>3.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>6.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>3.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.91</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.54</v>
+        <v>4.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.2</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.75</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>1.74</v>
       </c>
-      <c r="O3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
         <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.17</v>
+        <v>2.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>3.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,10 +921,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.17</v>
+        <v>1.19</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
         <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,49 +1040,49 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.55</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.91</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>6.6</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.54</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>2.91</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>3.68</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.35</v>
+        <v>3.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -921,49 +921,49 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.55</v>
       </c>
-      <c r="U4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
         <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1055,34 +1055,34 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>2.91</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>3.68</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>6.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>3.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.99</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.91</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.65</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>5.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.54</v>
+        <v>4.35</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -671,25 +671,25 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="U2" t="n">
         <v>1.44</v>
       </c>
       <c r="V2" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,7 +698,7 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
         <v>3.9</v>
@@ -713,13 +713,13 @@
         <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -897,64 +897,64 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
         <v>4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
         <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
         <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF4" t="n">
         <v>2.14</v>
@@ -963,7 +963,7 @@
         <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.95</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1147,10 +1147,10 @@
         <v>2.91</v>
       </c>
       <c r="P6" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
@@ -1195,10 +1195,10 @@
         <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
         <v>1.56</v>
@@ -1263,7 +1263,7 @@
         <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
         <v>2.48</v>
@@ -1278,7 +1278,7 @@
         <v>3.28</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
         <v>1.52</v>
@@ -1293,10 +1293,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
         <v>1.65</v>
@@ -1305,7 +1305,7 @@
         <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
         <v>1.44</v>
@@ -1317,7 +1317,7 @@
         <v>2.26</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="n">
         <v>1.21</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
         <v>4.4</v>
@@ -823,10 +823,10 @@
         <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
         <v>3.04</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>4.4</v>
@@ -912,7 +912,7 @@
         <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
         <v>1.28</v>
@@ -939,25 +939,25 @@
         <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
         <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
         <v>1.21</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>2.1</v>
@@ -1040,34 +1040,34 @@
         <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="U5" t="n">
         <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA5" t="n">
         <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD5" t="n">
         <v>1.33</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>2.89</v>
+        <v>3.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="V6" t="n">
-        <v>6.6</v>
+        <v>5.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.99</v>
+        <v>2.45</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.3</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="P7" t="n">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>5.45</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>3.54</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
         <v>2.9</v>
@@ -683,10 +683,10 @@
         <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V2" t="n">
         <v>5.8</v>
@@ -698,22 +698,22 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
         <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
         <v>1.62</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
@@ -1174,16 +1174,16 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC6" t="n">
         <v>2.45</v>
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
         <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -1293,10 +1293,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
         <v>1.8</v>
@@ -1314,7 +1314,7 @@
         <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.91</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.21</v>
+        <v>3.91</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
         <v>4.4</v>
@@ -912,58 +912,58 @@
         <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.62</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.81</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
         <v>1.21</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.28</v>
+        <v>3.64</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>4.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.35</v>
+        <v>5.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1254,67 +1254,67 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.1</v>
       </c>
-      <c r="N7" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>5.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -686,10 +686,10 @@
         <v>2.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -701,19 +701,19 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.62</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>3.91</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="P3" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
         <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AF3" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.91</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
         <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="N6" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
         <v>4.1</v>
@@ -1180,10 +1180,10 @@
         <v>5.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>2.17</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>2.84</v>
@@ -1299,10 +1299,10 @@
         <v>4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>2.68</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -671,7 +671,7 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
         <v>2.9</v>
@@ -680,16 +680,16 @@
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="U2" t="n">
         <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -701,7 +701,7 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76</v>
@@ -716,10 +716,10 @@
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
         <v>3.02</v>
@@ -817,16 +817,16 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC3" t="n">
         <v>2.9</v>
@@ -835,10 +835,10 @@
         <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.87</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.62</v>
       </c>
-      <c r="M4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4.4</v>
+        <v>2.09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1144,40 +1144,40 @@
         <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
         <v>1.65</v>
       </c>
       <c r="V6" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.65</v>
@@ -1186,22 +1186,22 @@
         <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AD6" t="n">
         <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.2</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1263,40 +1263,40 @@
         <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="P7" t="n">
-        <v>2.39</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
         <v>1.8</v>
@@ -1305,19 +1305,19 @@
         <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
         <v>1.56</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>5.47</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -802,49 +802,49 @@
         <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD3" t="n">
         <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>5.2</v>
+        <v>6.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M5" t="n">
         <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.47</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M6" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
         <v>4.2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AA6" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.21</v>
+        <v>2.61</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.51</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>4.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.61</v>
+        <v>2.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M3" t="n">
         <v>3.85</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O3" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.47</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>2.09</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH5" t="n">
         <v>2.3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -671,16 +671,16 @@
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
         <v>2.58</v>
@@ -698,7 +698,7 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
         <v>3.9</v>
@@ -713,13 +713,13 @@
         <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M3" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>5.2</v>
+        <v>6.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.66666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>5.47</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -921,49 +921,49 @@
         <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M5" t="n">
         <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.47</v>
+        <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M6" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>4.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.51</v>
+        <v>2.21</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.61</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.6875</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z7" t="n">
         <v>4.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,76 +778,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
         <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>4.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V3" t="n">
-        <v>6.05</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.58</v>
+        <v>3.22</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>3.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46007.66666666666</v>
+        <v>46007.58333333334</v>
       </c>
     </row>
     <row r="4">
@@ -906,40 +906,40 @@
         <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="P4" t="n">
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V4" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AA4" t="n">
         <v>1.75</v>
@@ -951,13 +951,13 @@
         <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
         <v>1.22</v>
@@ -1025,7 +1025,7 @@
         <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
         <v>2.38</v>
@@ -1034,31 +1034,31 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.62</v>
@@ -1070,7 +1070,7 @@
         <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
         <v>1.6</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.22</v>
       </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="Z6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="V6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46007.6875</v>
+        <v>46007.66666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1254,28 +1254,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
         <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
         <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
         <v>2.44</v>
@@ -1293,36 +1293,155 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
         <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
         <v>1.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI7" s="3" t="n">
+        <v>46007.6875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Winterthur</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46007.6875</v>
       </c>
     </row>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -701,13 +701,13 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC2" t="n">
         <v>2.74</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.46</v>
@@ -796,16 +796,16 @@
         <v>4.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -817,22 +817,22 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.22</v>
+        <v>3.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC3" t="n">
         <v>3.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
@@ -841,10 +841,10 @@
         <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.58333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>3.91</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
         <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>4.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1052,25 +1052,25 @@
         <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
         <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC5" t="n">
         <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
         <v>1.6</v>
@@ -1082,7 +1082,7 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>6.05</v>
+        <v>5.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.46</v>
@@ -823,10 +823,10 @@
         <v>3.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.53</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.21</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.74</v>
+        <v>5.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
         <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>4.21</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>5.4</v>
+        <v>1.74</v>
       </c>
       <c r="O6" t="n">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
         <v>2.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.91</v>
+        <v>4.21</v>
       </c>
       <c r="M4" t="n">
         <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
         <v>3.18</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.21</v>
+        <v>3.91</v>
       </c>
       <c r="M6" t="n">
         <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>2.23</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.49</v>
       </c>
-      <c r="V7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AB7" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.61</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z8" t="n">
         <v>4.2</v>
       </c>
-      <c r="M8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.62</v>
-      </c>
       <c r="AA8" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -701,31 +701,31 @@
         <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
         <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z7" t="n">
         <v>4.2</v>
       </c>
-      <c r="M7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.62</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>5.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -677,13 +677,13 @@
         <v>3.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
         <v>1.43</v>
@@ -713,19 +713,19 @@
         <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AG2" t="n">
         <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -787,40 +787,40 @@
         <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.79</v>
+        <v>3.83</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T3" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -832,7 +832,7 @@
         <v>3.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
         <v>1.73</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.21</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>1.74</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.17</v>
       </c>
-      <c r="Z4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,40 +1016,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.4</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>2.07</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1061,28 +1061,28 @@
         <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
         <v>2.25</v>
@@ -1153,19 +1153,19 @@
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="n">
         <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1180,28 +1180,28 @@
         <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
         <v>2.93</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
         <v>1.87</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1269,7 +1269,7 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -1308,19 +1308,19 @@
         <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.59</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1382,13 +1382,13 @@
         <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
         <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1406,7 +1406,7 @@
         <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
         <v>1.04</v>
@@ -1424,16 +1424,16 @@
         <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
         <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AG8" t="n">
         <v>1.89</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.16</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>5.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.61</v>
+        <v>2.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.62</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="n">
         <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
@@ -683,10 +683,10 @@
         <v>3.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
         <v>5.8</v>
@@ -698,19 +698,19 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
         <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD2" t="n">
         <v>1.4</v>
@@ -722,10 +722,10 @@
         <v>2.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="P3" t="n">
         <v>2.25</v>
@@ -799,16 +799,16 @@
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -820,25 +820,25 @@
         <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC3" t="n">
         <v>3.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
         <v>1.29</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,40 +897,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
         <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>2.06</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T4" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
         <v>1.04</v>
@@ -939,31 +939,31 @@
         <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD4" t="n">
         <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>2.06</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.62</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.16</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.44</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>5.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.61</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
         <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
         <v>3.05</v>
@@ -704,10 +704,10 @@
         <v>3.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>2.75</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.43</v>
@@ -823,10 +823,10 @@
         <v>3.28</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.53</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.63</v>
+        <v>2.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>2.03</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>5.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M6" t="n">
         <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.06</v>
+        <v>4.12</v>
       </c>
       <c r="P6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
         <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>1.22</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>5.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.22</v>
       </c>
-      <c r="S8" t="n">
-        <v>4</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z8" t="n">
-        <v>5.62</v>
+        <v>4.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>2.61</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
         <v>3.6</v>
@@ -912,7 +912,7 @@
         <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -936,19 +936,19 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.93</v>
+        <v>2.83</v>
       </c>
       <c r="AD4" t="n">
         <v>1.36</v>
@@ -960,7 +960,7 @@
         <v>2.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
         <v>1.25</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="O5" t="n">
         <v>2.03</v>
@@ -1058,31 +1058,31 @@
         <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF5" t="n">
         <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>4.12</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
@@ -1159,16 +1159,16 @@
         <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
@@ -1180,13 +1180,13 @@
         <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
         <v>1.4</v>
@@ -1198,10 +1198,10 @@
         <v>2.25</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>4.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
         <v>2.1</v>
@@ -1278,13 +1278,13 @@
         <v>3.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="W7" t="n">
         <v>1.14</v>
@@ -1293,28 +1293,28 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.84</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.14</v>
       </c>
       <c r="AD7" t="n">
         <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AG7" t="n">
         <v>1.25</v>
@@ -1373,64 +1373,64 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.33</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
         <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
         <v>3.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
         <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.38</v>
+        <v>4.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AF8" t="n">
         <v>2.41</v>
@@ -1439,7 +1439,7 @@
         <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -686,46 +686,46 @@
         <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AF2" t="n">
         <v>2.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>2.43</v>
@@ -793,16 +793,16 @@
         <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.83</v>
+        <v>4.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>2.77</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U3" t="n">
         <v>1.38</v>
@@ -814,31 +814,31 @@
         <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE3" t="n">
         <v>1.78</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
         <v>1.29</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>4.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>5.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,46 +1016,46 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.85</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.42</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
@@ -1067,22 +1067,22 @@
         <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>3.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.65</v>
+        <v>5.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.48</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.43</v>
@@ -823,10 +823,10 @@
         <v>3.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
         <v>3.3</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>4.85</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>2.03</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.42</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,46 +1016,46 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>4.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>5.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
@@ -1067,22 +1067,22 @@
         <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.48</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V7" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>4.65</v>
+        <v>5.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.58</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -683,13 +683,13 @@
         <v>3.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
         <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>6.2</v>
+        <v>6.15</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
@@ -698,31 +698,31 @@
         <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z2" t="n">
         <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD2" t="n">
         <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
         <v>1.44</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>4.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>5.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.41</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,46 +1016,46 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>4.85</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.42</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
@@ -1067,22 +1067,22 @@
         <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1254,55 +1254,55 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4</v>
+        <v>3.63</v>
       </c>
       <c r="M7" t="n">
-        <v>4.05</v>
+        <v>3.76</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
         <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>2.1</v>
@@ -1311,16 +1311,16 @@
         <v>1.67</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.48</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U8" t="n">
         <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1.21</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.15</v>
+        <v>4.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
         <v>1.59</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>3.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>4.85</v>
+        <v>1.84</v>
       </c>
       <c r="O4" t="n">
-        <v>2.03</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.42</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.3</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,46 +1016,46 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.55</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>4.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>5.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
@@ -1067,22 +1067,22 @@
         <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="AD5" t="n">
         <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.69</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.5</v>
+        <v>4.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>3.69</v>
       </c>
       <c r="P8" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.42</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.47</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -668,7 +668,7 @@
         <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P2" t="n">
         <v>2.3</v>
@@ -677,31 +677,31 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="U2" t="n">
         <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>6.15</v>
+        <v>5.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.76</v>
@@ -710,10 +710,10 @@
         <v>1.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
         <v>1.57</v>
@@ -725,7 +725,7 @@
         <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -787,22 +787,22 @@
         <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="P3" t="n">
         <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.76</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
         <v>1.38</v>
@@ -811,16 +811,16 @@
         <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.85</v>
@@ -832,19 +832,19 @@
         <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.58333333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.35</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>1.84</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>2.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>4.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,40 +1016,40 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.53</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
@@ -1061,28 +1061,28 @@
         <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.3</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.55</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>4.35</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>2.19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.42</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.54</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.69</v>
+        <v>2.58</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>4.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M4" t="n">
         <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>2.13</v>
+        <v>3.57</v>
       </c>
       <c r="P4" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.45</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V4" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -936,34 +936,34 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
         <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.57</v>
+        <v>4.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>4.35</v>
+        <v>2.13</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>2.4</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.69</v>
-      </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.95</v>
+        <v>5.65</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
@@ -1177,31 +1177,31 @@
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.57</v>
+        <v>2.13</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>4.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V4" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
@@ -936,34 +936,34 @@
         <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
         <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>4.35</v>
+        <v>3.57</v>
       </c>
       <c r="P5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.4</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.69</v>
-      </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V5" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.13</v>
+        <v>4.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.04</v>
@@ -1177,31 +1177,31 @@
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -677,57 +612,18 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
-        <v>3.08</v>
+        <v>1.94</v>
       </c>
       <c r="T2" t="n">
-        <v>2.61</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF2" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46007.375</v>
       </c>
     </row>
@@ -796,57 +692,18 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.85</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46007.58333333334</v>
       </c>
     </row>
@@ -915,57 +772,18 @@
         <v>4.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V4" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF4" t="n">
         <v>2.04</v>
       </c>
-      <c r="AG4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -1034,57 +852,18 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF5" t="n">
         <v>2.22</v>
       </c>
-      <c r="AG5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -1153,57 +932,18 @@
         <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.83</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>1.87</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -1272,57 +1012,18 @@
         <v>2.19</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>1.51</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF7" t="n">
         <v>2.51</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46007.6875</v>
       </c>
     </row>
@@ -1391,57 +1092,18 @@
         <v>3.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>1.54</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF8" t="n">
         <v>2.43</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="V8" s="3" t="n">
         <v>46007.6875</v>
       </c>
     </row>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -612,18 +677,57 @@
         <v>2.9</v>
       </c>
       <c r="R2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1.76</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
         <v>1.94</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AC2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.57</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
         <v>2.25</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="AG2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46007.375</v>
       </c>
     </row>
@@ -692,18 +796,57 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1.85</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AB3" t="n">
         <v>1.85</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AC3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.87</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AF3" t="n">
         <v>1.95</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="AG3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46007.58333333334</v>
       </c>
     </row>
@@ -772,18 +915,57 @@
         <v>4.45</v>
       </c>
       <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA4" t="n">
         <v>1.75</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
         <v>1.95</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AC4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.76</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AF4" t="n">
         <v>2.04</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="AG4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -852,18 +1034,57 @@
         <v>2.3</v>
       </c>
       <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.62</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AB5" t="n">
         <v>2.15</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AC5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.65</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AF5" t="n">
         <v>2.22</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="AG5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -932,18 +1153,57 @@
         <v>2.4</v>
       </c>
       <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.83</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AB6" t="n">
         <v>1.87</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AC6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="AG6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
       </c>
     </row>
@@ -968,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -994,36 +1254,75 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.19</v>
+        <v>3.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.51</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="V7" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
       </c>
     </row>
@@ -1048,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1074,36 +1373,75 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.02</v>
+        <v>2.19</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="V8" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46007.6875</v>
       </c>
     </row>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -642,90 +642,90 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V2" t="n">
         <v>5.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46007.375</v>
@@ -787,13 +787,13 @@
         <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -802,10 +802,10 @@
         <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -817,7 +817,7 @@
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
         <v>3.4</v>
@@ -832,19 +832,19 @@
         <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.58333333334</v>
@@ -906,13 +906,13 @@
         <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.45</v>
+        <v>4.61</v>
       </c>
       <c r="R4" t="n">
         <v>1.3</v>
@@ -921,7 +921,7 @@
         <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U4" t="n">
         <v>1.5</v>
@@ -933,13 +933,13 @@
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
         <v>1.75</v>
@@ -954,7 +954,7 @@
         <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
         <v>2.04</v>
@@ -963,7 +963,7 @@
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1025,13 +1025,13 @@
         <v>1.62</v>
       </c>
       <c r="O5" t="n">
-        <v>3.57</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R5" t="n">
         <v>1.29</v>
@@ -1040,7 +1040,7 @@
         <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
         <v>1.53</v>
@@ -1058,7 +1058,7 @@
         <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
         <v>1.62</v>
@@ -1067,19 +1067,19 @@
         <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD5" t="n">
         <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
         <v>1.17</v>
@@ -1144,34 +1144,34 @@
         <v>1.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4.35</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="T6" t="n">
         <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.22</v>
@@ -1192,16 +1192,16 @@
         <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.16</v>
+        <v>3.63</v>
       </c>
       <c r="M7" t="n">
-        <v>3.33</v>
+        <v>3.76</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.58</v>
+        <v>4.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="V7" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.73</v>
+        <v>5.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.63</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
-        <v>3.76</v>
+        <v>3.33</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="O3" t="n">
         <v>2.3</v>
@@ -802,16 +802,16 @@
         <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
@@ -832,19 +832,19 @@
         <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46007.58333333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.61</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V4" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="W4" t="n">
         <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="AG4" t="n">
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46007.66666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
-        <v>6.05</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AG6" t="n">
         <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.63</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4.26</v>
+        <v>2.86</v>
       </c>
       <c r="P7" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="U7" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.34</v>
+        <v>3.96</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.27</v>
+        <v>2.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.33</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>5.9</v>
+        <v>4.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.68</v>
+        <v>2.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>3.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="U7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.44</v>
       </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46007.6875</v>
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.85</v>
+        <v>2.37</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>2.86</v>
       </c>
       <c r="P8" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.21</v>
+        <v>2.68</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.29</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46007.6875</v>

--- a/jogos_2025-12-16.xlsx
+++ b/jogos_2025-12-16.xlsx
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="O5" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.26</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46007.66666666666</v>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AF6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46007.66666666666</v>
